--- a/data_raw/OS-Inventory-list-20260202.xlsx
+++ b/data_raw/OS-Inventory-list-20260202.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gjanee-local/work/UCSB-Library-OSSSI/data_raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xiuqili/Documents/GitHub/Open-Science-Inventory/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDB9023-E5C9-DC45-97A9-0A91D637B691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11965D71-3466-FC47-A6D0-2FD984A395C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="1020" windowWidth="30240" windowHeight="18880" xr2:uid="{1509BDA8-4FD2-7641-BB7D-D0BB426F409D}"/>
   </bookViews>
@@ -76,9 +76,6 @@
     <t>Protocols.io</t>
   </si>
   <si>
-    <t>Engagement</t>
-  </si>
-  <si>
     <t>Open Source Meetup</t>
   </si>
   <si>
@@ -335,6 +332,9 @@
   </si>
   <si>
     <t>LibGuides (OS-themed)</t>
+  </si>
+  <si>
+    <t>Engagement &amp; Community</t>
   </si>
 </sst>
 </file>
@@ -797,27 +797,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="C2" s="12">
         <v>1</v>
@@ -829,10 +829,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="12">
         <v>2</v>
@@ -844,10 +844,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="12">
         <v>3</v>
@@ -859,10 +859,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="12">
         <v>4</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="12">
         <v>5</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="12">
         <v>6</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="12">
         <v>7</v>
@@ -919,41 +919,41 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C9" s="4">
         <v>8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="4">
         <v>9</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>7</v>
@@ -963,14 +963,14 @@
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
@@ -980,17 +980,17 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4">
         <v>12</v>
@@ -1002,83 +1002,83 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4">
         <v>13</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="4">
         <v>14</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="8">
         <v>15</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="8">
         <v>16</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>2</v>
@@ -1087,10 +1087,10 @@
         <v>17</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
@@ -1099,19 +1099,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="8">
         <v>18</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>8</v>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>3</v>
@@ -1129,10 +1129,10 @@
         <v>19</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>4</v>
@@ -1150,10 +1150,10 @@
         <v>20</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>8</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>5</v>
@@ -1171,10 +1171,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>6</v>
@@ -1192,31 +1192,31 @@
         <v>22</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="8">
         <v>23</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
@@ -1225,61 +1225,61 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C25" s="8">
         <v>24</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="8">
         <v>25</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="8">
         <v>26</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>7</v>
@@ -1288,19 +1288,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C28" s="8">
         <v>27</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>12</v>
@@ -1318,10 +1318,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>8</v>
@@ -1330,19 +1330,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="8">
         <v>29</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>9</v>
@@ -1360,10 +1360,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>8</v>
@@ -1372,84 +1372,84 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32" s="8">
         <v>31</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C33" s="6">
         <v>32</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" s="6">
         <v>33</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="6">
         <v>34</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>8</v>
@@ -1460,272 +1460,272 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" s="6">
         <v>35</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C37" s="6">
         <v>36</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="F37" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" s="6">
         <v>37</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" s="6">
         <v>38</v>
       </c>
       <c r="D39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40" s="6">
         <v>39</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="6">
         <v>40</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="6">
         <v>41</v>
       </c>
       <c r="D42" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C43" s="6">
         <v>42</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>7</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C44" s="6">
         <v>43</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="6">
         <v>44</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="10">
         <v>45</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="10">
         <v>46</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>8</v>
@@ -1734,19 +1734,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C48" s="10">
         <v>47</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>7</v>
@@ -1755,40 +1755,40 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="10">
         <v>48</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G49" s="9"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C50" s="10">
         <v>49</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>7</v>
@@ -1799,19 +1799,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C51" s="10">
         <v>50</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>8</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>10</v>
@@ -1829,52 +1829,52 @@
         <v>51</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G52" s="9"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53" s="10">
         <v>52</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G53" s="9"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>14</v>
       </c>
       <c r="C54" s="10">
         <v>53</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>8</v>
@@ -1883,19 +1883,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" s="10">
         <v>54</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>8</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>11</v>
@@ -1913,13 +1913,13 @@
         <v>55</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G56" s="9"/>
     </row>
